--- a/data/trans_dic/IP13_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas</t>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,59</t>
+          <t>1,32; 6,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,82</t>
+          <t>1,53; 7,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,73</t>
+          <t>1,88; 5,57</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,4</t>
+          <t>2,37; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,31</t>
+          <t>2,68; 7,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,53</t>
+          <t>3,08; 6,4</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,45</t>
+          <t>1,54; 6,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,26</t>
+          <t>2,34; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,18</t>
+          <t>2,6; 6,25</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 8,85</t>
+          <t>2,44; 8,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,6</t>
+          <t>3,63; 10,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,18</t>
+          <t>3,88; 8,04</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,46</t>
+          <t>2,86; 5,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,2</t>
+          <t>3,45; 6,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,51</t>
+          <t>3,61; 5,43</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3690</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4939</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8630</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1550; 8047</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2130; 10342</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4832; 14311</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8480</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11263</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19743</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4514; 13738</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6828; 18088</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13736; 28521</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6616</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8505</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15121</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2929; 11533</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4338; 14105</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9741; 23422</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11845</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19916</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4103; 14038</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6583; 19124</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13539; 28059</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>26858</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36553</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>63411</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>19011; 36467</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26271; 47471</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51509; 77482</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,86</t>
+          <t>1,24; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,4</t>
+          <t>1,37; 7,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,57</t>
+          <t>1,82; 5,72</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,21</t>
+          <t>2,58; 7,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,09</t>
+          <t>2,6; 7,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,4</t>
+          <t>3,03; 6,2</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,08</t>
+          <t>1,57; 6,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,61</t>
+          <t>2,43; 8,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,25</t>
+          <t>2,48; 6,1</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,36</t>
+          <t>2,6; 8,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 10,55</t>
+          <t>3,77; 10,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,04</t>
+          <t>3,77; 8,27</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,48</t>
+          <t>2,84; 5,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,24</t>
+          <t>3,61; 6,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,43</t>
+          <t>3,59; 5,46</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1550; 8047</t>
+          <t>1455; 7277</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2130; 10342</t>
+          <t>1916; 10342</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4832; 14311</t>
+          <t>4668; 14692</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4514; 13738</t>
+          <t>4911; 14595</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6828; 18088</t>
+          <t>6643; 18368</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13736; 28521</t>
+          <t>13511; 27614</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2929; 11533</t>
+          <t>2986; 11888</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4338; 14105</t>
+          <t>4507; 14920</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9741; 23422</t>
+          <t>9302; 22865</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4103; 14038</t>
+          <t>4363; 14557</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6583; 19124</t>
+          <t>6834; 18953</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13539; 28059</t>
+          <t>13158; 28881</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19011; 36467</t>
+          <t>18874; 35042</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26271; 47471</t>
+          <t>27485; 48516</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51509; 77482</t>
+          <t>51166; 77859</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,2</t>
+          <t>1,72; 8,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,4</t>
+          <t>1,37; 6,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,72</t>
+          <t>1,97; 6,05</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,66</t>
+          <t>2,85; 7,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,2</t>
+          <t>2,32; 6,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,2</t>
+          <t>3,04; 6,54</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,27</t>
+          <t>2,17; 7,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 8,05</t>
+          <t>2,11; 8,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,1</t>
+          <t>2,75; 6,68</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,67</t>
+          <t>3,91; 10,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,46</t>
+          <t>2,54; 8,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,27</t>
+          <t>3,88; 8,0</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,27</t>
+          <t>3,71; 6,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,37</t>
+          <t>3,01; 5,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,46</t>
+          <t>3,72; 5,6</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8644</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1455; 7277</t>
+          <t>2153; 10902</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1916; 10342</t>
+          <t>1660; 8054</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4668; 14692</t>
+          <t>4848; 14920</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>18739</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4911; 14595</t>
+          <t>6767; 18394</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6643; 18368</t>
+          <t>4273; 12757</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13511; 27614</t>
+          <t>12808; 27560</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>14310</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2986; 11888</t>
+          <t>3645; 12929</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4507; 14920</t>
+          <t>3298; 12557</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9302; 22865</t>
+          <t>8926; 21691</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>18781</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4363; 14557</t>
+          <t>6615; 17760</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6834; 18953</t>
+          <t>4249; 14067</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13158; 28881</t>
+          <t>13053; 26911</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>34234</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18874; 35042</t>
+          <t>26014; 44933</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27485; 48516</t>
+          <t>18945; 35016</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51166; 77859</t>
+          <t>49431; 74402</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R2_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R2_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 8,7</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 6,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,97; 6,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2,85; 7,75</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,32; 6,92</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3,04; 6,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,17; 7,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,11; 8,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2,75; 6,68</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3,91; 10,49</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2,54; 8,42</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3,88; 8,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,71; 6,42</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3,01; 5,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3,72; 5,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.03825238162682192</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.03178505153136664</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.03507511285763368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4796</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3848</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8644</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.01717113470195853</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01370889636090111</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.01967079013704831</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2153; 10902</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1660; 8054</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4848; 14920</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.08696218712025915</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.06652550909181627</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.06054366688920367</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.04645935329771256</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.04185243748221976</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.04444432607585322</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>11020</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7718</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18739</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.02852936779393332</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.0231705737526072</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.03037740575496591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6767; 18394</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4273; 12757</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12808; 27560</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.07754260561448845</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.06917784738795375</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.06536823067097124</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.04398450358881962</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.04420991594394622</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.04409299496081202</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7404</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6906</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14310</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.02165446477753616</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.02111152553131371</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.02750318988478232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3645; 12929</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3298; 12557</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8926; 21691</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.07680107580996609</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.08039060551257599</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.06683492874461787</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.06502627783869341</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.04646773154649551</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.05580854056956307</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>11014</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7767</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18781</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.03905438255251753</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.02541918338334946</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.03878885559357448</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6615; 17760</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>4249; 14067</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>13053; 26911</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1048532988481456</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.08415968291217611</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.07996908131525057</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.04888587545735911</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.04172648469626149</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04549864135286093</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>34234</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>26239</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>60473</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.03714727948428735</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.03012678807661155</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.03719056314963567</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>26014; 44933</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>18945; 35016</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>49431; 74402</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.06416299531432031</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.05568360607174268</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.05597802633771914</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4796</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3848</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>8644</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2153</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1660</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>4848</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>10902</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>8054</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>14920</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>11020</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>7718</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>18739</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>6767</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4273</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>12808</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>18394</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>12757</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>27560</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>7404</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>6906</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>14310</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>3645</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>3298</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>8926</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>12929</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>12557</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>21691</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>11014</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>7767</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>18781</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>6615</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>4249</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>13053</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>17760</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>14067</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>26911</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>34234</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>26239</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>60473</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>26014</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>18945</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>49431</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>44933</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>35016</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>74402</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>